--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$86</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2700" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3213" uniqueCount="634">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T07:17:44+00:00</t>
+    <t>2023-05-10T08:50:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Global (Whole world)</t>
+    <t>World</t>
   </si>
   <si>
     <t>Description</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -240,13 +240,13 @@
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
-    <t>Mapping: HL7 v2 Mapping</t>
+    <t>Mapping: FiveWs Pattern Mapping</t>
+  </si>
+  <si>
+    <t>Mapping: HL7 V2 Mapping</t>
   </si>
   <si>
     <t>Mapping: RIM Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: FiveWs Pattern Mapping</t>
   </si>
   <si>
     <t>Mapping: Quality Improvement and Clinical Knowledge (QUICK)</t>
@@ -278,10 +278,13 @@
     <t>Request</t>
   </si>
   <si>
+    <t>clinical.general</t>
+  </si>
+  <si>
     <t>ORC</t>
   </si>
   <si>
-    <t>Act[moodCode&lt;=INT]</t>
+    <t>Entity, Role, or Act,Act[moodCode&lt;=INT]</t>
   </si>
   <si>
     <t>ServiceRequest.id</t>
@@ -303,7 +306,7 @@
     <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
   </si>
   <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>Within the context of the FHIR RESTful interactions, the resource has an id except for cases like the create and conditional update. Otherwise, the use of the resouce id depends on the given use case.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -342,7 +345,7 @@
     <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
   </si>
   <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of its narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -364,13 +367,13 @@
     <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>IETF language tag for a human language</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/all-languages|5.0.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -393,10 +396,14 @@
     <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
   </si>
   <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>Contained resources do not have a narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dom-6
+</t>
   </si>
   <si>
     <t>Act.text?</t>
@@ -416,13 +423,17 @@
     <t>Contained, inline Resources</t>
   </si>
   <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, nor can they have their own independent transaction scope. This is allowed to be a Parameters resource if and only if it is referenced by a resource that provides context/meaning.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags in their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>dom-2
+dom-4dom-3dom-5</t>
   </si>
   <si>
     <t>N/A</t>
@@ -442,7 +453,7 @@
     <t>Additional content defined by implementations</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
@@ -461,11 +472,11 @@
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R5/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -484,7 +495,7 @@
     <t>Identifiers assigned to this order instance by the orderer and/or the receiver and/or order fulfiller.</t>
   </si>
   <si>
-    <t>The identifier.type element is used to distinguish between the identifiers assigned by the orderer (known as the 'Placer' in HL7 v2) and the producer of the observations in response to the order (known as the 'Filler' in HL7 v2).  For further discussion and examples see the resource notes section below.</t>
+    <t>The identifier.type element is used to distinguish between the identifiers assigned by the orderer (known as the 'Placer' in HL7 V2) and the producer of the observations in response to the order (known as the 'Filler' in HL7 V2).  For further discussion and examples see the resource notes section below.</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:system}
@@ -500,15 +511,15 @@
     <t>Request.identifier</t>
   </si>
   <si>
-    <t>ORC.2, ORC.3, RF1-6 / RF1-11,</t>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>ORC-2, ORC-3, RF1-6 / RF1-11,</t>
   </si>
   <si>
     <t>.identifier</t>
   </si>
   <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
     <t>ClinicalStatement.identifier</t>
   </si>
   <si>
@@ -522,241 +533,246 @@
   </si>
   <si>
     <t>ServiceRequest.identifier.id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.use</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|5.0.0</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type.coding</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type.coding.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.coding.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type.coding.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.coding.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type.coding.system</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should be an absolute reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type.coding.version</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.coding.version</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type.coding.code</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cod-1
 </t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.use</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type.coding</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type.coding.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.coding.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type.coding.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.coding.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type.coding.system</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type.coding.version</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type.coding.code</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -862,7 +878,7 @@
     <t>The namespace for the identifier value</t>
   </si>
   <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+    <t>Establishes the namespace for the value - that is, an absolute URL that describes a set values that are unique.</t>
   </si>
   <si>
     <t>Identifier.system is always case sensitive.</t>
@@ -898,13 +914,17 @@
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [http://hl7.org/fhir/StructureDefinition/rendered-value](http://hl7.org/fhir/extensions/StructureDefinition-rendered-value.html)). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>123456</t>
   </si>
   <si>
     <t>Identifier.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ident-1
+</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -979,7 +999,7 @@
     <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this ServiceRequest.</t>
   </si>
   <si>
-    <t>Note: This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
+    <t>The PlanDefinition resource is used to describe series, sequences, or groups of actions to be taken, while the ActivityDefinition resource is used to define each specific step or activity to be performed. More information can be found in the [Boundaries and Relationships](http://hl7.org/fhir/R5/plandefinition.html#12.23.2) section for PlanDefinition.</t>
   </si>
   <si>
     <t>Request.instantiatesCanonical</t>
@@ -1026,7 +1046,7 @@
     <t>Request.basedOn</t>
   </si>
   <si>
-    <t>ORC.8 (plus others)</t>
+    <t>ORC-8 (plus others)</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=FLFS].target</t>
@@ -1052,7 +1072,7 @@
     <t>Request.replaces</t>
   </si>
   <si>
-    <t>Handled by message location of ORC (ORC.1=RO or RU)</t>
+    <t>Handled by message location of ORC (ORC-1=RO or RU)</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=RPLC].target</t>
@@ -1080,7 +1100,7 @@
     <t>Request.groupIdentifier</t>
   </si>
   <si>
-    <t>ORC.4</t>
+    <t>ORC-4</t>
   </si>
   <si>
     <t>.inboundRelationship(typeCode=COMP].source[moodCode=INT].identifier</t>
@@ -1095,34 +1115,34 @@
     <t>The status of the order.</t>
   </si>
   <si>
-    <t>The status is generally fully in the control of the requester - they determine whether the order is draft or active and, after it has been activated, competed, cancelled or suspended. States relating to the activities of the performer are reflected on either the corresponding event (see [Event Pattern](event.html) for general discussion) or using the [Task](http://hl7.org/fhir/R4/task.html) resource.</t>
+    <t>The status is generally fully in the control of the requester - they determine whether the order is draft or active and, after it has been activated, competed, revoked or placed on-hold. States relating to the activities of the performer are reflected on either the corresponding event (see [Event Pattern](event.html) for general discussion) or using the [Task](http://hl7.org/fhir/R5/task.html) resource.</t>
   </si>
   <si>
     <t>The status of a service order.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/request-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/request-status|5.0.0</t>
   </si>
   <si>
     <t>Request.status</t>
   </si>
   <si>
-    <t>ORC.5,RF1-1</t>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>ORC-5,RF1-1</t>
   </si>
   <si>
     <t>.status</t>
   </si>
   <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
     <t>Action.currentStatus</t>
   </si>
   <si>
     <t>ServiceRequest.intent</t>
   </si>
   <si>
-    <t>proposal | plan | directive | order | original-order | reflex-order | filler-order | instance-order | option</t>
+    <t>proposal | plan | directive | order +</t>
   </si>
   <si>
     <t>Whether the request is a proposal, plan, an original order or a reflex order.</t>
@@ -1137,18 +1157,18 @@
     <t>The kind of service request.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/request-intent|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/request-intent|5.0.0</t>
   </si>
   <si>
     <t>Request.intent</t>
   </si>
   <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
     <t>.moodCode (nuances beyond PRP/PLAN/RQO would need to be elsewhere)</t>
   </si>
   <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
     <t>ServiceRequest.category</t>
   </si>
   <si>
@@ -1194,19 +1214,19 @@
     <t>Identifies the level of importance to be assigned to actioning the request.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/request-priority|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/request-priority|5.0.0</t>
   </si>
   <si>
     <t>Request.priority</t>
   </si>
   <si>
+    <t>FiveWs.grade</t>
+  </si>
+  <si>
     <t>TQ1.9, RF1-2</t>
   </si>
   <si>
     <t>.priorityCode</t>
-  </si>
-  <si>
-    <t>FiveWs.grade</t>
   </si>
   <si>
     <t>ServiceRequest.doNotPerform</t>
@@ -1240,10 +1260,14 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">CodeableReference(ActivityDefinition|PlanDefinition)
+</t>
+  </si>
+  <si>
     <t>What is being requested/ordered</t>
   </si>
   <si>
-    <t>A code that identifies a particular service (i.e., procedure, diagnostic investigation, or panel of investigations) that have been requested.</t>
+    <t>A code or reference that identifies a particular service (i.e., procedure, diagnostic investigation, or panel of investigations) that have been requested.</t>
   </si>
   <si>
     <t>Many laboratory and radiology procedure codes embed the specimen/organ system in the test order name, for example,  serum or serum/plasma glucose, or a chest x-ray. The specimen might not be recorded separately from the test code.</t>
@@ -1252,18 +1276,22 @@
     <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-test-types</t>
   </si>
   <si>
+    <t xml:space="preserve">prr-1
+</t>
+  </si>
+  <si>
     <t>Request.code</t>
   </si>
   <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
     <t>PR1-3 / OBR-4  (varies by domain)</t>
   </si>
   <si>
     <t>.code</t>
   </si>
   <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
     <t>Procedure.procedureCode</t>
   </si>
   <si>
@@ -1273,13 +1301,47 @@
     <t>ServiceRequest.code.extension</t>
   </si>
   <si>
-    <t>ServiceRequest.code.coding</t>
-  </si>
-  <si>
-    <t>ServiceRequest.code.text</t>
+    <t>ServiceRequest.code.concept</t>
+  </si>
+  <si>
+    <t>Reference to a concept (by class)</t>
+  </si>
+  <si>
+    <t>A reference to a concept - e.g. the information is identified by its general class to the degree of precision found in the terminology.</t>
+  </si>
+  <si>
+    <t>CodeableReference.concept</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.concept.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.concept.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.concept.coding</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.concept.text</t>
   </si>
   <si>
     <t>Test Type</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference
+</t>
+  </si>
+  <si>
+    <t>Reference to a resource (by instance)</t>
+  </si>
+  <si>
+    <t>A reference to a resource the provides exact details about the information being referenced.</t>
+  </si>
+  <si>
+    <t>CodeableReference.reference</t>
   </si>
   <si>
     <t>ServiceRequest.orderDetail</t>
@@ -1289,6 +1351,10 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
     <t>Additional order information</t>
   </si>
   <si>
@@ -1298,17 +1364,92 @@
     <t>For information from the medical record intended to support the delivery of the requested services, use the `supportingInformation` element.</t>
   </si>
   <si>
-    <t>Codified order entry details which are based on order context.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prr-1
+    <t>NTE</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.parameterFocus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableReference(Device|DeviceDefinition|DeviceRequest|SupplyRequest|Medication|MedicationRequest|BiologicallyDerivedProduct|Substance)
 </t>
   </si>
   <si>
-    <t>NTE</t>
+    <t>The context of the order details by reference</t>
+  </si>
+  <si>
+    <t>Indicates the context of the order details by reference.</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.parameter</t>
+  </si>
+  <si>
+    <t>The parameter details for the service being requested</t>
+  </si>
+  <si>
+    <t>The parameter details for the service being requested.</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.parameter.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.parameter.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.parameter.modifierExtension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.parameter.code</t>
+  </si>
+  <si>
+    <t>The detail of the order being requested</t>
+  </si>
+  <si>
+    <t>A value representing the additional detail or instructions for the order (e.g., catheter insertion, body elevation, descriptive device configuration and/or setting instructions).</t>
+  </si>
+  <si>
+    <t>Codes for order detail parameters.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail-parameter-code</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.parameter.value[x]</t>
+  </si>
+  <si>
+    <t>Quantity
+RatioRangebooleanCodeableConceptstringPeriod</t>
+  </si>
+  <si>
+    <t>The value for the order detail</t>
+  </si>
+  <si>
+    <t>Indicates a value for the order detail.</t>
+  </si>
+  <si>
+    <t>CodeableConcept values are indented to express concepts that would normally be coded - when a code is not available for a concept, CodeableConcept.text can be used. When the data is a text or not a single identifiable concept, string should be used.</t>
   </si>
   <si>
     <t>ServiceRequest.quantity[x]</t>
@@ -1346,16 +1487,32 @@
     <t>Request.subject</t>
   </si>
   <si>
+    <t>FiveWs.subject[x]</t>
+  </si>
+  <si>
     <t>PID</t>
   </si>
   <si>
     <t>.participation[typeCode=SBJ].role</t>
   </si>
   <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
     <t>ClinicalStatement.subject</t>
+  </si>
+  <si>
+    <t>ServiceRequest.focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Resource)
+</t>
+  </si>
+  <si>
+    <t>What the service request is about, when it is not about the subject of record</t>
+  </si>
+  <si>
+    <t>The actual focus of a service request when it is not the subject of record representing something or someone associated with the subject such as a spouse, parent, fetus, or donor. The focus of a service request could also be an existing condition,  an intervention, the subject's diet,  another service request on the subject,  or a body structure such as tumor or implanted device.</t>
+  </si>
+  <si>
+    <t>participation[typeCode=SBJ]</t>
   </si>
   <si>
     <t>ServiceRequest.encounter</t>
@@ -1378,13 +1535,13 @@
     <t>Request.encounter</t>
   </si>
   <si>
+    <t>FiveWs.context</t>
+  </si>
+  <si>
     <t>PV1</t>
   </si>
   <si>
     <t>.inboundRelationship(typeCode=COMP].source[classCode&lt;=PCPR, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>FiveWs.context</t>
   </si>
   <si>
     <t>ClinicalStatement.encounter</t>
@@ -1414,13 +1571,13 @@
     <t>Request.occurrence[x]</t>
   </si>
   <si>
+    <t>FiveWs.planned</t>
+  </si>
+  <si>
     <t>TQ1/TQ2, OBR-7/OBR-8</t>
   </si>
   <si>
     <t>.effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.planned</t>
   </si>
   <si>
     <t>Procedure.procedureSchedule</t>
@@ -1477,13 +1634,13 @@
     <t>Request.authoredOn</t>
   </si>
   <si>
-    <t>ORC.9,  RF1-7 / RF1-9</t>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>ORC-9,  RF1-7 / RF1-9</t>
   </si>
   <si>
     <t>.participation[typeCode=AUT].time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
   </si>
   <si>
     <t>Proposal.proposedAtTime</t>
@@ -1512,13 +1669,13 @@
     <t>Request.requester</t>
   </si>
   <si>
-    <t>ORC.12, PRT</t>
+    <t>FiveWs.author</t>
+  </si>
+  <si>
+    <t>ORC-12, PRT</t>
   </si>
   <si>
     <t>.participation[typeCode=AUT].role</t>
-  </si>
-  <si>
-    <t>FiveWs.author</t>
   </si>
   <si>
     <t>ClinicalStatement.statementAuthor</t>
@@ -1549,13 +1706,13 @@
     <t>Request.performerType</t>
   </si>
   <si>
-    <t>PRT, RF!-3</t>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>PRT, RF1-3</t>
   </si>
   <si>
     <t>.participation[typeCode=PRF].role[scoper.determinerCode=KIND].code</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
   </si>
   <si>
     <t>ServiceRequest.performer</t>
@@ -1575,7 +1732,7 @@
     <t>The desired performer for doing the requested service.  For example, the surgeon, dermatopathologist, endoscopist, etc.</t>
   </si>
   <si>
-    <t>If multiple performers are present, it is interpreted as a list of *alternative* performers without any preference regardless of order.  If order of preference is needed use the [request-performerOrder extension](http://hl7.org/fhir/R4/extension-request-performerorder.html).  Use CareTeam to represent a group of performers (for example, Practitioner A *and* Practitioner B).</t>
+    <t>If multiple performers are present, it is interpreted as a list of *alternative* performers without any preference regardless of order.  If order of preference is needed use the [http://hl7.org/fhir/StructureDefinition/request-performerOrder](http://hl7.org/fhir/extensions/StructureDefinition-request-performerOrder.html).  Use CareTeam to represent a group of performers (for example, Practitioner A *and* Practitioner B).</t>
   </si>
   <si>
     <t>Request.performer</t>
@@ -1587,7 +1744,11 @@
     <t>.participation[typeCode=PRF].role[scoper.determinerCode=INSTANCE]</t>
   </si>
   <si>
-    <t>ServiceRequest.locationCode</t>
+    <t>ServiceRequest.location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableReference(Location)
+</t>
   </si>
   <si>
     <t>Requested location</t>
@@ -1605,84 +1766,38 @@
     <t>.participation[typeCode=LOC].role[scoper.determinerCode=KIND].code</t>
   </si>
   <si>
-    <t>ServiceRequest.locationReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Location)
+    <t>ServiceRequest.reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableReference(Observation)
 </t>
   </si>
   <si>
-    <t>A reference to the the preferred location(s) where the procedure should actually happen. E.g. at home or nursing day care center.</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=LOC].role[scoper.determinerCode=INSTANCE]</t>
-  </si>
-  <si>
-    <t>ServiceRequest.reasonCode</t>
-  </si>
-  <si>
     <t>Explanation/Justification for procedure or service</t>
   </si>
   <si>
     <t>An explanation or justification for why this service is being requested in coded or textual form.   This is often for billing purposes.  May relate to the resources referred to in `supportingInfo`.</t>
   </si>
   <si>
-    <t>This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all.   Use `CodeableConcept.text` element if the data is free (uncoded) text as shown in the [CT Scan example](servicerequest-example-di.html).</t>
-  </si>
-  <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-reason-for-assessment</t>
-  </si>
-  <si>
-    <t>Request.reasonCode</t>
-  </si>
-  <si>
-    <t>ORC.16, RF1-10</t>
+    <t>This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all. To be as specific as possible,  a reference to  *Observation* or *Condition* should be used if available.  Otherwise, use `concept.text` element if the data is free (uncoded) text as shown in the [CT Scan example](servicerequest-example-di.html).</t>
+  </si>
+  <si>
+    <t>SNOMED CT Condition/Problem/Diagnosis Codes</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
+  </si>
+  <si>
+    <t>Request.reason</t>
+  </si>
+  <si>
+    <t>FiveWs.why[x]</t>
+  </si>
+  <si>
+    <t>ORC-16, RF1-10</t>
   </si>
   <si>
     <t>.reasonCode</t>
-  </si>
-  <si>
-    <t>FiveWs.why[x]</t>
-  </si>
-  <si>
-    <t>ServiceRequest.reasonCode.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.reasonCode.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.reasonCode.coding</t>
-  </si>
-  <si>
-    <t>ServiceRequest.reasonCode.text</t>
-  </si>
-  <si>
-    <t>Reason for testing</t>
-  </si>
-  <si>
-    <t>ServiceRequest.reasonReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport|DocumentReference)
-</t>
-  </si>
-  <si>
-    <t>Explanation/Justification for service or service</t>
-  </si>
-  <si>
-    <t>Indicates another resource that provides a justification for why this service is being requested.   May relate to the resources referred to in `supportingInfo`.</t>
-  </si>
-  <si>
-    <t>This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all.    To be as specific as possible,  a reference to  *Observation* or *Condition* should be used if available.  Otherwise when referencing  *DiagnosticReport*  it should contain a finding  in `DiagnosticReport.conclusion` and/or `DiagnosticReport.conclusionCode`.   When using a reference to *DocumentReference*, the target document should contain clear findings language providing the relevant reason for this service request.  Use  the CodeableConcept text element in `ServiceRequest.reasonCode` if the data is free (uncoded) text as shown in the [CT Scan example](servicerequest-example-di.html).</t>
-  </si>
-  <si>
-    <t>Request.reasonReference</t>
-  </si>
-  <si>
-    <t>ORC.16</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=RSON].target</t>
   </si>
   <si>
     <t>ServiceRequest.insurance</t>
@@ -1714,7 +1829,7 @@
 AOE</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">CodeableReference(Resource)
 </t>
   </si>
   <si>
@@ -1749,7 +1864,7 @@
     <t>One or more specimens that the laboratory procedure will use.</t>
   </si>
   <si>
-    <t>Many diagnostic procedures need a specimen, but the request itself is not actually about the specimen. This element is for when the diagnostic is requested on already existing specimens and the request points to the specimen it applies to.    Conversely, if the request is entered first with an unknown specimen, then the [Specimen](http://hl7.org/fhir/R4/specimen.html) resource points to the ServiceRequest.</t>
+    <t>The purpose of the ServiceRequest.specimen is to reflect the actual specimen that the requested test/procedure is asked to be performed on, whether the lab already has it or not.  References to specimens for purposes other than to perform a test/procedure on should be made using the ServiceRequest.supportingInfo or the Specimen.parent where the Specimen.parent would enable descendency and ServiceRequest.supportingInfo a general reference for context.</t>
   </si>
   <si>
     <t>SPM</t>
@@ -1765,28 +1880,49 @@
 </t>
   </si>
   <si>
-    <t>Location on Body</t>
+    <t>Coded location on Body</t>
   </si>
   <si>
     <t>Anatomic location where the procedure should be performed. This is the target site.</t>
   </si>
   <si>
-    <t>Only used if not implicit in the code found in ServiceRequest.code.  If the use case requires BodySite to be handled as a separate resource instead of an inline coded element (e.g. to identify and track separately)  then use the standard extension [procedure-targetBodyStructure](http://hl7.org/fhir/R4/extension-procedure-targetbodystructure.html).</t>
+    <t>Only used if not implicit in the code found in ServiceRequest.code.  If the use case requires BodySite to be handled as a separate resource instead of an inline coded element (e.g. to identify and track separately)  then use the standard extension [http://hl7.org/fhir/StructureDefinition/procedure-targetBodyStructure](http://hl7.org/fhir/extensions/StructureDefinition-procedure-targetBodyStructure.html).</t>
   </si>
   <si>
     <t>Knowing where the procedure is performed is important for tracking if multiple sites are possible.</t>
   </si>
   <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
+    <t>SNOMED CT Body site concepts</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
+    <t xml:space="preserve">bdystr-1
+</t>
+  </si>
+  <si>
     <t>targetSiteCode</t>
   </si>
   <si>
     <t>Procedure.targetBodySite</t>
+  </si>
+  <si>
+    <t>ServiceRequest.bodyStructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">locationStructure
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(BodyStructure)
+</t>
+  </si>
+  <si>
+    <t>BodyStructure-based location on the body</t>
+  </si>
+  <si>
+    <t>Procedure.targetBodyStructure</t>
   </si>
   <si>
     <t>ServiceRequest.note</t>
@@ -1818,6 +1954,22 @@
   </si>
   <si>
     <t>.text</t>
+  </si>
+  <si>
+    <t>ServiceRequest.patientInstruction.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.patientInstruction.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.patientInstruction.modifierExtension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.patientInstruction.instruction[x]</t>
+  </si>
+  <si>
+    <t>markdown
+Reference(DocumentReference)</t>
   </si>
   <si>
     <t>ServiceRequest.relevantHistory</t>
@@ -1990,7 +2142,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -2077,77 +2229,85 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B20" t="s" s="2">
+      <c r="B21" t="s" s="2">
         <v>36</v>
       </c>
     </row>
@@ -2158,11 +2318,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO72"/>
+  <dimension ref="A1:AO86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="53.35546875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="48.078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="53.71484375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="53.71484375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="20.203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="44.00390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -2171,7 +2331,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="105.421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="135.5703125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2192,14 +2352,14 @@
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="35.71484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="45.1484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="85.41796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="163.4453125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="85.41796875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="163.4453125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="66.88671875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -2437,7 +2597,7 @@
         <v>87</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>81</v>
@@ -2445,10 +2605,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2459,7 +2619,7 @@
         <v>79</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>81</v>
@@ -2468,19 +2628,19 @@
         <v>81</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2530,13 +2690,13 @@
         <v>81</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>81</v>
@@ -2562,10 +2722,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2576,7 +2736,7 @@
         <v>79</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>81</v>
@@ -2585,16 +2745,16 @@
         <v>81</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2645,19 +2805,19 @@
         <v>81</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>81</v>
@@ -2677,10 +2837,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2691,28 +2851,28 @@
         <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2762,19 +2922,19 @@
         <v>81</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>81</v>
@@ -2794,10 +2954,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2808,7 +2968,7 @@
         <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>81</v>
@@ -2820,16 +2980,16 @@
         <v>81</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2855,13 +3015,13 @@
         <v>81</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>81</v>
@@ -2879,19 +3039,19 @@
         <v>81</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>81</v>
@@ -2911,21 +3071,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>81</v>
@@ -2937,16 +3097,16 @@
         <v>81</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2996,19 +3156,19 @@
         <v>81</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>81</v>
@@ -3017,10 +3177,10 @@
         <v>81</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>81</v>
@@ -3028,14 +3188,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -3054,16 +3214,16 @@
         <v>81</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3113,7 +3273,7 @@
         <v>81</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>79</v>
@@ -3122,7 +3282,7 @@
         <v>80</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="AJ8" t="s" s="2">
         <v>81</v>
@@ -3134,10 +3294,10 @@
         <v>81</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>81</v>
@@ -3145,14 +3305,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3171,16 +3331,16 @@
         <v>81</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3230,7 +3390,7 @@
         <v>81</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -3242,7 +3402,7 @@
         <v>81</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>81</v>
@@ -3251,10 +3411,10 @@
         <v>81</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>81</v>
@@ -3262,14 +3422,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3282,25 +3442,25 @@
         <v>81</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>81</v>
@@ -3349,7 +3509,7 @@
         <v>81</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -3361,7 +3521,7 @@
         <v>81</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>81</v>
@@ -3370,10 +3530,10 @@
         <v>81</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>81</v>
@@ -3381,10 +3541,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3392,7 +3552,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>80</v>
@@ -3404,19 +3564,19 @@
         <v>81</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3454,19 +3614,19 @@
         <v>81</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3478,33 +3638,33 @@
         <v>81</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>81</v>
@@ -3514,28 +3674,28 @@
         <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3585,7 +3745,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3597,30 +3757,30 @@
         <v>81</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3631,7 +3791,7 @@
         <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>81</v>
@@ -3643,13 +3803,13 @@
         <v>81</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>163</v>
+        <v>92</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3700,16 +3860,16 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>81</v>
+        <v>169</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>81</v>
@@ -3721,10 +3881,10 @@
         <v>81</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>81</v>
@@ -3732,14 +3892,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3758,16 +3918,16 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3805,19 +3965,19 @@
         <v>81</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3829,7 +3989,7 @@
         <v>81</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>81</v>
@@ -3838,10 +3998,10 @@
         <v>81</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>81</v>
@@ -3849,10 +4009,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3863,31 +4023,31 @@
         <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>81</v>
@@ -3912,13 +4072,13 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>181</v>
+        <v>114</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
@@ -3936,31 +4096,31 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>81</v>
+        <v>187</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>81</v>
@@ -3968,10 +4128,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3982,7 +4142,7 @@
         <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>81</v>
@@ -3991,22 +4151,22 @@
         <v>81</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>81</v>
@@ -4031,13 +4191,13 @@
         <v>81</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>81</v>
@@ -4055,31 +4215,31 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>197</v>
+        <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>81</v>
+        <v>187</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>81</v>
@@ -4087,10 +4247,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4101,7 +4261,7 @@
         <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>81</v>
@@ -4113,13 +4273,13 @@
         <v>81</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>163</v>
+        <v>92</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4170,16 +4330,16 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>81</v>
+        <v>169</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>81</v>
@@ -4191,10 +4351,10 @@
         <v>81</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>81</v>
@@ -4202,14 +4362,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4228,16 +4388,16 @@
         <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4275,19 +4435,19 @@
         <v>81</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4299,7 +4459,7 @@
         <v>81</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>81</v>
@@ -4308,10 +4468,10 @@
         <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>81</v>
@@ -4319,10 +4479,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4342,22 +4502,22 @@
         <v>81</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -4406,7 +4566,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4418,19 +4578,19 @@
         <v>81</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>210</v>
+        <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>81</v>
@@ -4438,10 +4598,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4452,7 +4612,7 @@
         <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>81</v>
@@ -4464,13 +4624,13 @@
         <v>81</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>163</v>
+        <v>92</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4521,16 +4681,16 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>81</v>
+        <v>169</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>81</v>
@@ -4542,10 +4702,10 @@
         <v>81</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>81</v>
@@ -4553,14 +4713,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4579,16 +4739,16 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4626,19 +4786,19 @@
         <v>81</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4650,7 +4810,7 @@
         <v>81</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>81</v>
@@ -4659,10 +4819,10 @@
         <v>81</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>81</v>
@@ -4670,10 +4830,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4684,7 +4844,7 @@
         <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>81</v>
@@ -4693,22 +4853,22 @@
         <v>81</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -4718,7 +4878,7 @@
         <v>81</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>81</v>
@@ -4757,31 +4917,31 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>81</v>
+        <v>227</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>81</v>
@@ -4789,10 +4949,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4803,7 +4963,7 @@
         <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>81</v>
@@ -4812,19 +4972,19 @@
         <v>81</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>163</v>
+        <v>230</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4874,31 +5034,31 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>232</v>
+        <v>81</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>81</v>
+        <v>236</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>81</v>
@@ -4906,10 +5066,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4920,7 +5080,7 @@
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>81</v>
@@ -4929,20 +5089,20 @@
         <v>81</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4952,7 +5112,7 @@
         <v>81</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>81</v>
@@ -4991,31 +5151,31 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>240</v>
+        <v>81</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>81</v>
+        <v>245</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>81</v>
@@ -5023,10 +5183,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5037,7 +5197,7 @@
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>81</v>
@@ -5046,20 +5206,20 @@
         <v>81</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>163</v>
+        <v>230</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5069,7 +5229,7 @@
         <v>81</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>81</v>
@@ -5108,31 +5268,31 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>249</v>
+        <v>81</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>81</v>
+        <v>254</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>81</v>
@@ -5140,10 +5300,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5154,7 +5314,7 @@
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>81</v>
@@ -5163,22 +5323,22 @@
         <v>81</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5227,31 +5387,31 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>259</v>
+        <v>81</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>81</v>
+        <v>264</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>81</v>
@@ -5259,10 +5419,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5273,7 +5433,7 @@
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>81</v>
@@ -5282,22 +5442,22 @@
         <v>81</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>163</v>
+        <v>230</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5307,7 +5467,7 @@
         <v>81</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>81</v>
@@ -5346,31 +5506,31 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>269</v>
+        <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>81</v>
+        <v>274</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>81</v>
@@ -5378,10 +5538,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5389,10 +5549,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>81</v>
@@ -5401,35 +5561,35 @@
         <v>81</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>81</v>
@@ -5465,31 +5625,31 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>280</v>
+        <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>81</v>
+        <v>285</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>81</v>
@@ -5497,10 +5657,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5511,28 +5671,28 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>163</v>
+        <v>230</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5546,7 +5706,7 @@
         <v>81</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>81</v>
@@ -5582,31 +5742,31 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>81</v>
+        <v>293</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>81</v>
+        <v>295</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>81</v>
@@ -5614,10 +5774,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5628,7 +5788,7 @@
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>81</v>
@@ -5637,16 +5797,16 @@
         <v>81</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5697,31 +5857,31 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>297</v>
+        <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>81</v>
+        <v>303</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>81</v>
@@ -5729,10 +5889,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5743,7 +5903,7 @@
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>81</v>
@@ -5752,19 +5912,19 @@
         <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5814,31 +5974,31 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>306</v>
+        <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>81</v>
+        <v>312</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>81</v>
@@ -5846,10 +6006,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5869,19 +6029,19 @@
         <v>81</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5931,7 +6091,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5943,19 +6103,19 @@
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>314</v>
+        <v>81</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>81</v>
+        <v>320</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>81</v>
@@ -5963,10 +6123,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5986,19 +6146,19 @@
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6048,7 +6208,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6060,19 +6220,19 @@
         <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>81</v>
@@ -6080,14 +6240,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6103,16 +6263,16 @@
         <v>81</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6163,7 +6323,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6175,19 +6335,19 @@
         <v>81</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>327</v>
+        <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>81</v>
+        <v>333</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>81</v>
@@ -6195,14 +6355,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6218,16 +6378,16 @@
         <v>81</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6278,7 +6438,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6290,19 +6450,19 @@
         <v>81</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>335</v>
+        <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>81</v>
+        <v>341</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>81</v>
@@ -6310,21 +6470,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>81</v>
@@ -6333,22 +6493,22 @@
         <v>81</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6397,31 +6557,31 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>344</v>
+        <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>81</v>
+        <v>350</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
@@ -6429,10 +6589,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6440,31 +6600,31 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6490,66 +6650,66 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>181</v>
+        <v>114</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="Z37" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AA37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>346</v>
-      </c>
       <c r="AG37" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6557,31 +6717,31 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6592,7 +6752,7 @@
         <v>81</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>81</v>
@@ -6607,55 +6767,55 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>181</v>
+        <v>114</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="AG38" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>132</v>
+        <v>370</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>365</v>
+        <v>135</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>81</v>
@@ -6663,10 +6823,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6686,22 +6846,22 @@
         <v>81</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6726,31 +6886,31 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6762,19 +6922,19 @@
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>81</v>
@@ -6782,10 +6942,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6796,7 +6956,7 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
@@ -6805,16 +6965,16 @@
         <v>81</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6822,7 +6982,7 @@
         <v>81</v>
       </c>
       <c r="Q40" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="R40" t="s" s="2">
         <v>81</v>
@@ -6843,55 +7003,55 @@
         <v>81</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>181</v>
+        <v>114</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="Z40" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AA40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>377</v>
-      </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>81</v>
@@ -6899,10 +7059,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6913,106 +7073,106 @@
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I41" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="P41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q41" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="R41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH41" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="J41" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K41" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="P41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q41" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="R41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>394</v>
+        <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>81</v>
+        <v>399</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>81</v>
@@ -7020,21 +7180,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>81</v>
@@ -7043,19 +7203,19 @@
         <v>81</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>188</v>
+        <v>402</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7081,64 +7241,64 @@
         <v>81</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>181</v>
+        <v>114</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AA42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>395</v>
-      </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>81</v>
+        <v>407</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>405</v>
+        <v>412</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7149,7 +7309,7 @@
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>81</v>
@@ -7161,13 +7321,13 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>163</v>
+        <v>92</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7218,16 +7378,16 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>81</v>
+        <v>169</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>81</v>
@@ -7239,10 +7399,10 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>81</v>
@@ -7250,14 +7410,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7276,16 +7436,16 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7323,19 +7483,19 @@
         <v>81</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7347,7 +7507,7 @@
         <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>81</v>
@@ -7356,10 +7516,10 @@
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>81</v>
@@ -7367,10 +7527,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7381,7 +7541,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>81</v>
@@ -7390,23 +7550,19 @@
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>205</v>
+        <v>416</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
@@ -7454,31 +7610,31 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>209</v>
+        <v>418</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>210</v>
+        <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>211</v>
+        <v>81</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>81</v>
@@ -7486,10 +7642,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7500,7 +7656,7 @@
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>81</v>
@@ -7509,23 +7665,19 @@
         <v>81</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>163</v>
+        <v>92</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>263</v>
+        <v>166</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>81</v>
       </c>
@@ -7534,7 +7686,7 @@
         <v>81</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>410</v>
+        <v>81</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>81</v>
@@ -7573,31 +7725,31 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>268</v>
+        <v>168</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>81</v>
+        <v>169</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>269</v>
+        <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>270</v>
+        <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>81</v>
@@ -7605,14 +7757,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>412</v>
+        <v>137</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7628,19 +7780,19 @@
         <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>188</v>
+        <v>138</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>413</v>
+        <v>139</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>414</v>
+        <v>173</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>415</v>
+        <v>141</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7666,31 +7818,31 @@
         <v>81</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>372</v>
+        <v>81</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>416</v>
+        <v>81</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>417</v>
+        <v>81</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>81</v>
+        <v>175</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>81</v>
+        <v>176</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>411</v>
+        <v>177</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7699,33 +7851,33 @@
         <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>418</v>
+        <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>419</v>
+        <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>403</v>
+        <v>81</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>405</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7736,7 +7888,7 @@
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>81</v>
@@ -7745,20 +7897,22 @@
         <v>81</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>421</v>
+        <v>206</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>422</v>
+        <v>207</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="O48" t="s" s="2">
-        <v>424</v>
+        <v>210</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7807,31 +7961,31 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>420</v>
+        <v>211</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>419</v>
+        <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>425</v>
+        <v>212</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>81</v>
@@ -7839,10 +7993,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7850,10 +8004,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>81</v>
@@ -7862,19 +8016,23 @@
         <v>81</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>427</v>
+        <v>230</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>428</v>
+        <v>267</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>81</v>
       </c>
@@ -7883,7 +8041,7 @@
         <v>81</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>81</v>
@@ -7922,53 +8080,53 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>426</v>
+        <v>272</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>430</v>
+        <v>81</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>431</v>
+        <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>432</v>
+        <v>273</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>433</v>
+        <v>274</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>434</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>436</v>
+        <v>81</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>81</v>
@@ -7977,16 +8135,16 @@
         <v>81</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8037,53 +8195,53 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>440</v>
+        <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>441</v>
+        <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>442</v>
+        <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>443</v>
+        <v>135</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>444</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>81</v>
@@ -8092,18 +8250,20 @@
         <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -8140,83 +8300,83 @@
         <v>81</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AC51" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>81</v>
+        <v>407</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>451</v>
+        <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>452</v>
+        <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>453</v>
+        <v>435</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>454</v>
+        <v>81</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>455</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>446</v>
+        <v>81</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>458</v>
+        <v>230</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>448</v>
+        <v>166</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>449</v>
+        <v>167</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8267,53 +8427,53 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>445</v>
+        <v>168</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>81</v>
+        <v>169</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>451</v>
+        <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>452</v>
+        <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>453</v>
+        <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>454</v>
+        <v>170</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>455</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>459</v>
+        <v>437</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>459</v>
+        <v>437</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>81</v>
@@ -8322,18 +8482,20 @@
         <v>81</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>460</v>
+        <v>138</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>461</v>
+        <v>139</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -8358,13 +8520,13 @@
         <v>81</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>372</v>
+        <v>81</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>463</v>
+        <v>81</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>464</v>
+        <v>81</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
@@ -8382,19 +8544,19 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>459</v>
+        <v>177</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>81</v>
@@ -8403,53 +8565,57 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>465</v>
+        <v>81</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>466</v>
+        <v>81</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>458</v>
+        <v>138</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>469</v>
+        <v>440</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>441</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
       </c>
@@ -8497,53 +8663,53 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>467</v>
+        <v>442</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>471</v>
+        <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>472</v>
+        <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>473</v>
+        <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>474</v>
+        <v>135</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>475</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>477</v>
+        <v>81</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>81</v>
@@ -8552,20 +8718,18 @@
         <v>81</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>478</v>
+        <v>444</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>479</v>
+        <v>445</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>81</v>
@@ -8614,53 +8778,53 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>482</v>
+        <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>483</v>
+        <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>484</v>
+        <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>485</v>
+        <v>81</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>486</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>487</v>
+        <v>447</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>487</v>
+        <v>447</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>488</v>
+        <v>81</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>81</v>
@@ -8669,20 +8833,18 @@
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>188</v>
+        <v>431</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>489</v>
+        <v>448</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>491</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8707,13 +8869,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>372</v>
+        <v>81</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>492</v>
+        <v>81</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>493</v>
+        <v>81</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -8731,31 +8893,31 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>487</v>
+        <v>447</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>494</v>
+        <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>495</v>
+        <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>496</v>
+        <v>81</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>497</v>
+        <v>81</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
@@ -8763,21 +8925,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>498</v>
+        <v>450</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>498</v>
+        <v>450</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>499</v>
+        <v>81</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>81</v>
@@ -8786,20 +8948,18 @@
         <v>81</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>501</v>
+        <v>166</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>503</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -8848,31 +9008,31 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>498</v>
+        <v>168</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>81</v>
+        <v>169</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>504</v>
+        <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>505</v>
+        <v>81</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>506</v>
+        <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>497</v>
+        <v>170</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>81</v>
@@ -8880,14 +9040,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>507</v>
+        <v>451</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>507</v>
+        <v>451</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8903,18 +9063,20 @@
         <v>81</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>188</v>
+        <v>138</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>508</v>
+        <v>139</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -8939,13 +9101,13 @@
         <v>81</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>372</v>
+        <v>81</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>510</v>
+        <v>81</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>511</v>
+        <v>81</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>81</v>
@@ -8963,7 +9125,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>507</v>
+        <v>177</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8975,7 +9137,7 @@
         <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>81</v>
@@ -8984,10 +9146,10 @@
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>512</v>
+        <v>81</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>497</v>
+        <v>170</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>81</v>
@@ -8995,14 +9157,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>513</v>
+        <v>452</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>513</v>
+        <v>452</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>81</v>
+        <v>439</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9015,22 +9177,26 @@
         <v>81</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>514</v>
+        <v>138</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>508</v>
+        <v>440</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>441</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>81</v>
       </c>
@@ -9078,7 +9244,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>513</v>
+        <v>442</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9090,7 +9256,7 @@
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>81</v>
@@ -9099,10 +9265,10 @@
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>516</v>
+        <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>497</v>
+        <v>135</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
@@ -9110,10 +9276,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>517</v>
+        <v>453</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>517</v>
+        <v>453</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9121,10 +9287,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>81</v>
@@ -9133,20 +9299,18 @@
         <v>81</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>518</v>
+        <v>454</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>520</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -9171,11 +9335,13 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="Y60" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="Z60" t="s" s="2">
-        <v>521</v>
+        <v>457</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -9193,31 +9359,31 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>517</v>
+        <v>453</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>522</v>
+        <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>523</v>
+        <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>524</v>
+        <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>525</v>
+        <v>81</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>81</v>
@@ -9225,10 +9391,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>526</v>
+        <v>458</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>526</v>
+        <v>458</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9236,10 +9402,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>81</v>
@@ -9248,18 +9414,20 @@
         <v>81</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>163</v>
+        <v>459</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>164</v>
+        <v>460</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>462</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -9308,19 +9476,19 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>166</v>
+        <v>458</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>81</v>
@@ -9329,7 +9497,7 @@
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>81</v>
@@ -9340,21 +9508,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>527</v>
+        <v>463</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>527</v>
+        <v>463</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
@@ -9363,21 +9531,21 @@
         <v>81</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>135</v>
+        <v>464</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>136</v>
+        <v>465</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>466</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" t="s" s="2">
+        <v>467</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
       </c>
@@ -9413,31 +9581,31 @@
         <v>81</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>171</v>
+        <v>81</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>174</v>
+        <v>463</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>81</v>
@@ -9446,10 +9614,10 @@
         <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>167</v>
+        <v>435</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>81</v>
+        <v>468</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>81</v>
@@ -9457,10 +9625,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>528</v>
+        <v>469</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>528</v>
+        <v>469</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9468,10 +9636,10 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>81</v>
@@ -9480,23 +9648,19 @@
         <v>81</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>204</v>
+        <v>470</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>205</v>
+        <v>471</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>81</v>
       </c>
@@ -9544,42 +9708,42 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>209</v>
+        <v>469</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>81</v>
+        <v>473</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>210</v>
+        <v>474</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>211</v>
+        <v>475</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>81</v>
+        <v>476</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>81</v>
+        <v>477</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>529</v>
+        <v>478</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>529</v>
+        <v>478</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9590,7 +9754,7 @@
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>81</v>
@@ -9599,23 +9763,19 @@
         <v>81</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>163</v>
+        <v>479</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>263</v>
+        <v>480</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>81</v>
       </c>
@@ -9624,7 +9784,7 @@
         <v>81</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>530</v>
+        <v>81</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>81</v>
@@ -9663,31 +9823,31 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>268</v>
+        <v>478</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>269</v>
+        <v>474</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>270</v>
+        <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>81</v>
+        <v>482</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>81</v>
@@ -9695,21 +9855,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>531</v>
+        <v>483</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>531</v>
+        <v>483</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>81</v>
+        <v>484</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>81</v>
@@ -9718,20 +9878,18 @@
         <v>81</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>532</v>
+        <v>485</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>533</v>
+        <v>486</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>535</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -9780,53 +9938,53 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>531</v>
+        <v>483</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>536</v>
+        <v>488</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>537</v>
+        <v>489</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>538</v>
+        <v>490</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>525</v>
+        <v>491</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>81</v>
+        <v>492</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>539</v>
+        <v>493</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>539</v>
+        <v>493</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>81</v>
+        <v>494</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>81</v>
@@ -9835,16 +9993,16 @@
         <v>81</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>540</v>
+        <v>495</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>541</v>
+        <v>496</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>542</v>
+        <v>497</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9883,87 +10041,85 @@
         <v>81</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="AC66" s="2"/>
       <c r="AD66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>81</v>
+        <v>176</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>539</v>
+        <v>493</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>543</v>
+        <v>499</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>544</v>
+        <v>500</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>545</v>
+        <v>501</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>81</v>
+        <v>502</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>81</v>
+        <v>503</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>546</v>
+        <v>504</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="C67" s="2"/>
+        <v>493</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="D67" t="s" s="2">
-        <v>547</v>
+        <v>494</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>548</v>
+        <v>506</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>549</v>
+        <v>496</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>551</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>81</v>
@@ -10012,42 +10168,42 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>546</v>
+        <v>493</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>552</v>
+        <v>499</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>553</v>
+        <v>500</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>554</v>
+        <v>501</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>81</v>
+        <v>502</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>81</v>
+        <v>503</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>555</v>
+        <v>507</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>555</v>
+        <v>507</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10055,10 +10211,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>81</v>
@@ -10067,20 +10223,18 @@
         <v>81</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>556</v>
+        <v>508</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>557</v>
+        <v>509</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>559</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -10105,13 +10259,13 @@
         <v>81</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>81</v>
+        <v>377</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>81</v>
+        <v>511</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>81</v>
+        <v>512</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>81</v>
@@ -10129,53 +10283,53 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>555</v>
+        <v>507</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>560</v>
+        <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>561</v>
+        <v>81</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>81</v>
+        <v>513</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>81</v>
+        <v>514</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>562</v>
+        <v>515</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>562</v>
+        <v>515</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>563</v>
+        <v>516</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>81</v>
@@ -10184,23 +10338,19 @@
         <v>81</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>188</v>
+        <v>506</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>564</v>
+        <v>517</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>567</v>
-      </c>
+        <v>518</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>81</v>
       </c>
@@ -10224,13 +10374,13 @@
         <v>81</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>372</v>
+        <v>81</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>568</v>
+        <v>81</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>569</v>
+        <v>81</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>81</v>
@@ -10248,73 +10398,75 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>562</v>
+        <v>515</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>81</v>
+        <v>519</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>560</v>
+        <v>520</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>570</v>
+        <v>521</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>81</v>
+        <v>522</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>571</v>
+        <v>523</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>572</v>
+        <v>524</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>572</v>
+        <v>524</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>81</v>
+        <v>525</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>573</v>
+        <v>526</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>50</v>
+        <v>527</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -10363,53 +10515,53 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>572</v>
+        <v>524</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>575</v>
+        <v>530</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>419</v>
+        <v>531</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>576</v>
+        <v>532</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>81</v>
+        <v>533</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>577</v>
+        <v>534</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>578</v>
+        <v>535</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>578</v>
+        <v>535</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>81</v>
+        <v>536</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>81</v>
@@ -10418,18 +10570,20 @@
         <v>81</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>579</v>
+        <v>537</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>538</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>539</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -10454,13 +10608,13 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>81</v>
+        <v>377</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>81</v>
+        <v>540</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>81</v>
+        <v>541</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -10478,31 +10632,31 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>578</v>
+        <v>535</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>81</v>
+        <v>542</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>419</v>
+        <v>543</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>581</v>
+        <v>544</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>81</v>
+        <v>545</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>81</v>
@@ -10510,21 +10664,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>582</v>
+        <v>546</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>582</v>
+        <v>546</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>81</v>
+        <v>547</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>81</v>
@@ -10533,19 +10687,19 @@
         <v>81</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>583</v>
+        <v>548</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>584</v>
+        <v>549</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>585</v>
+        <v>550</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>586</v>
+        <v>551</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10595,7 +10749,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>582</v>
+        <v>546</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10607,26 +10761,1656 @@
         <v>81</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="AL72" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AN76" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="AN72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO72" t="s" s="2">
+      <c r="AO76" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="P79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="P84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="AO86" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO72">
+  <autoFilter ref="A1:AO86">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10636,7 +12420,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI71">
+  <conditionalFormatting sqref="A2:AI85">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T08:50:20+00:00</t>
+    <t>2023-05-10T08:50:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T08:50:38+00:00</t>
+    <t>2023-05-10T09:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:32+00:00</t>
+    <t>2023-05-10T09:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:57+00:00</t>
+    <t>2023-05-10T09:45:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:45:15+00:00</t>
+    <t>2023-05-10T09:50:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:50:54+00:00</t>
+    <t>2023-05-10T10:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:15:35+00:00</t>
+    <t>2023-05-10T10:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:16:16+00:00</t>
+    <t>2023-05-10T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:21+00:00</t>
+    <t>2023-05-10T11:05:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:55+00:00</t>
+    <t>2023-05-10T11:27:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:27:56+00:00</t>
+    <t>2023-05-10T11:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:35:39+00:00</t>
+    <t>2023-05-10T12:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:05+00:00</t>
+    <t>2023-05-10T12:21:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:34+00:00</t>
+    <t>2023-05-11T06:47:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:47:47+00:00</t>
+    <t>2023-05-11T06:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:48:00+00:00</t>
+    <t>2023-05-11T06:54:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:54:20+00:00</t>
+    <t>2023-05-11T06:54:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:54:25+00:00</t>
+    <t>2023-05-11T08:35:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -498,7 +498,7 @@
     <t>The identifier.type element is used to distinguish between the identifiers assigned by the orderer (known as the 'Placer' in HL7 V2) and the producer of the observations in response to the order (known as the 'Filler' in HL7 V2).  For further discussion and examples see the resource notes section below.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:system}
+    <t xml:space="preserve">exists:system}
 </t>
   </si>
   <si>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>90</v>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:35:45+00:00</t>
+    <t>2023-05-11T08:41:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:41:43+00:00</t>
+    <t>2023-05-11T09:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -498,7 +498,7 @@
     <t>The identifier.type element is used to distinguish between the identifiers assigned by the orderer (known as the 'Placer' in HL7 V2) and the producer of the observations in response to the order (known as the 'Filler' in HL7 V2).  For further discussion and examples see the resource notes section below.</t>
   </si>
   <si>
-    <t xml:space="preserve">exists:system}
+    <t xml:space="preserve">value:system}
 </t>
   </si>
   <si>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>90</v>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:08:26+00:00</t>
+    <t>2023-05-11T09:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:17:12+00:00</t>
+    <t>2023-05-11T10:17:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -502,7 +502,7 @@
 </t>
   </si>
   <si>
-    <t>Slice based on the type of identifier</t>
+    <t>Slice based on the type of identifier.</t>
   </si>
   <si>
     <t>openAtEnd</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:25+00:00</t>
+    <t>2023-05-11T10:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:56+00:00</t>
+    <t>2023-05-11T10:34:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3677,7 +3677,7 @@
         <v>90</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>81</v>
@@ -3757,7 +3757,7 @@
         <v>81</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>157</v>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:34:10+00:00</t>
+    <t>2023-05-11T10:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3213" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3213" uniqueCount="633">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:41:58+00:00</t>
+    <t>2023-05-11T10:56:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -505,7 +505,7 @@
     <t>Slice based on the type of identifier.</t>
   </si>
   <si>
-    <t>openAtEnd</t>
+    <t>open</t>
   </si>
   <si>
     <t>Request.identifier</t>
@@ -565,9 +565,6 @@
   </si>
   <si>
     <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -3974,10 +3971,10 @@
         <v>81</v>
       </c>
       <c r="AE14" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -4009,10 +4006,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4038,16 +4035,16 @@
         <v>110</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>81</v>
@@ -4075,28 +4072,28 @@
         <v>114</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -4120,7 +4117,7 @@
         <v>135</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>81</v>
@@ -4128,10 +4125,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4154,19 +4151,19 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>81</v>
@@ -4191,31 +4188,31 @@
         <v>81</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -4236,10 +4233,10 @@
         <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>81</v>
@@ -4247,10 +4244,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4362,10 +4359,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4444,10 +4441,10 @@
         <v>81</v>
       </c>
       <c r="AE18" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4479,10 +4476,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4505,19 +4502,19 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -4566,7 +4563,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4587,10 +4584,10 @@
         <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>81</v>
@@ -4598,10 +4595,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4713,10 +4710,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4795,10 +4792,10 @@
         <v>81</v>
       </c>
       <c r="AE21" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4830,10 +4827,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4859,16 +4856,16 @@
         <v>104</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -4878,46 +4875,46 @@
         <v>81</v>
       </c>
       <c r="S22" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="T22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4938,10 +4935,10 @@
         <v>81</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>81</v>
@@ -4949,10 +4946,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4975,16 +4972,16 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5034,7 +5031,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -5055,10 +5052,10 @@
         <v>81</v>
       </c>
       <c r="AM23" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>81</v>
@@ -5066,10 +5063,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5095,14 +5092,14 @@
         <v>110</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -5151,7 +5148,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -5160,7 +5157,7 @@
         <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>102</v>
@@ -5172,10 +5169,10 @@
         <v>81</v>
       </c>
       <c r="AM24" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>81</v>
@@ -5183,10 +5180,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5209,17 +5206,17 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5229,46 +5226,46 @@
         <v>81</v>
       </c>
       <c r="S25" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="T25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5277,7 +5274,7 @@
         <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>102</v>
@@ -5289,10 +5286,10 @@
         <v>81</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>81</v>
@@ -5300,10 +5297,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5326,19 +5323,19 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5387,7 +5384,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5408,10 +5405,10 @@
         <v>81</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>81</v>
@@ -5419,10 +5416,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5445,19 +5442,19 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5467,46 +5464,46 @@
         <v>81</v>
       </c>
       <c r="S27" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5527,10 +5524,10 @@
         <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>81</v>
@@ -5538,10 +5535,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5567,65 +5564,65 @@
         <v>104</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T28" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="S28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T28" t="s" s="2">
+      <c r="U28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5646,10 +5643,10 @@
         <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>81</v>
@@ -5657,10 +5654,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5683,16 +5680,16 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5706,43 +5703,43 @@
         <v>81</v>
       </c>
       <c r="T29" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5751,7 +5748,7 @@
         <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>102</v>
@@ -5763,10 +5760,10 @@
         <v>81</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>81</v>
@@ -5774,10 +5771,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5800,13 +5797,13 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5857,7 +5854,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5878,10 +5875,10 @@
         <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>81</v>
@@ -5889,10 +5886,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5915,16 +5912,16 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5974,7 +5971,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5995,10 +5992,10 @@
         <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>81</v>
@@ -6006,10 +6003,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6032,16 +6029,16 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6091,7 +6088,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -6106,16 +6103,16 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AL32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>81</v>
@@ -6123,10 +6120,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6152,13 +6149,13 @@
         <v>104</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6208,7 +6205,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6223,16 +6220,16 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>81</v>
@@ -6240,14 +6237,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6266,13 +6263,13 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6323,7 +6320,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6338,16 +6335,16 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>81</v>
@@ -6355,14 +6352,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6381,13 +6378,13 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6438,7 +6435,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6453,16 +6450,16 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AL35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>81</v>
@@ -6470,14 +6467,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6499,16 +6496,16 @@
         <v>150</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6557,7 +6554,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6572,16 +6569,16 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AL36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AN36" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
@@ -6589,10 +6586,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6618,13 +6615,13 @@
         <v>110</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6653,11 +6650,11 @@
         <v>114</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>356</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
       </c>
@@ -6674,7 +6671,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>90</v>
@@ -6689,27 +6686,27 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>361</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6735,13 +6732,13 @@
         <v>110</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6752,7 +6749,7 @@
         <v>81</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>81</v>
@@ -6770,11 +6767,11 @@
         <v>114</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="Z38" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>368</v>
-      </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
       </c>
@@ -6791,7 +6788,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>90</v>
@@ -6806,16 +6803,16 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>135</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>81</v>
@@ -6823,10 +6820,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6849,19 +6846,19 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6886,14 +6883,14 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="Y39" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="Y39" t="s" s="2">
+      <c r="Z39" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>379</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
       </c>
@@ -6910,7 +6907,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6928,13 +6925,13 @@
         <v>81</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>81</v>
@@ -6942,10 +6939,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6971,10 +6968,10 @@
         <v>110</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6982,7 +6979,7 @@
         <v>81</v>
       </c>
       <c r="Q40" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="R40" t="s" s="2">
         <v>81</v>
@@ -7006,11 +7003,11 @@
         <v>114</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>387</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
       </c>
@@ -7027,7 +7024,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -7042,16 +7039,16 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>81</v>
@@ -7059,10 +7056,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7085,26 +7082,26 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="O41" t="s" s="2">
+      <c r="P41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q41" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="P41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q41" t="s" s="2">
-        <v>397</v>
-      </c>
       <c r="R41" t="s" s="2">
         <v>81</v>
       </c>
@@ -7148,7 +7145,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7163,16 +7160,16 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>81</v>
@@ -7180,14 +7177,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7206,16 +7203,16 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7245,7 +7242,7 @@
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>81</v>
@@ -7263,7 +7260,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7272,33 +7269,33 @@
         <v>90</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AM42" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>412</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7410,10 +7407,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7492,10 +7489,10 @@
         <v>81</v>
       </c>
       <c r="AE44" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7527,10 +7524,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7553,13 +7550,13 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7610,7 +7607,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7642,10 +7639,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7757,10 +7754,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7839,10 +7836,10 @@
         <v>81</v>
       </c>
       <c r="AE47" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7874,10 +7871,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7900,19 +7897,19 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7961,7 +7958,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7982,10 +7979,10 @@
         <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>81</v>
@@ -7993,10 +7990,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8019,19 +8016,19 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>81</v>
@@ -8041,7 +8038,7 @@
         <v>81</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>81</v>
@@ -8080,7 +8077,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8101,10 +8098,10 @@
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>81</v>
@@ -8112,10 +8109,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8138,13 +8135,13 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8195,7 +8192,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8227,14 +8224,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8253,16 +8250,16 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8312,7 +8309,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8321,7 +8318,7 @@
         <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>102</v>
@@ -8333,7 +8330,7 @@
         <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
@@ -8344,10 +8341,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8370,7 +8367,7 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>166</v>
@@ -8459,10 +8456,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8544,7 +8541,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8576,14 +8573,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8605,10 +8602,10 @@
         <v>138</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>141</v>
@@ -8663,7 +8660,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8695,10 +8692,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8721,13 +8718,13 @@
         <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8778,7 +8775,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8810,10 +8807,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8836,13 +8833,13 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8893,7 +8890,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>90</v>
@@ -8925,10 +8922,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8951,7 +8948,7 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L57" t="s" s="2">
         <v>166</v>
@@ -9040,10 +9037,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9125,7 +9122,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9157,14 +9154,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9186,10 +9183,10 @@
         <v>138</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>141</v>
@@ -9244,7 +9241,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9276,10 +9273,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9302,13 +9299,13 @@
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9335,14 +9332,14 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>457</v>
-      </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
       </c>
@@ -9359,7 +9356,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>90</v>
@@ -9391,10 +9388,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9417,16 +9414,16 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9476,7 +9473,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>90</v>
@@ -9508,10 +9505,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9534,17 +9531,17 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
@@ -9593,7 +9590,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9614,10 +9611,10 @@
         <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>81</v>
@@ -9625,10 +9622,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9651,13 +9648,13 @@
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9708,7 +9705,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>90</v>
@@ -9723,27 +9720,27 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AL63" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AM63" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="AM63" t="s" s="2">
+      <c r="AN63" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="AN63" t="s" s="2">
+      <c r="AO63" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>477</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9766,13 +9763,13 @@
         <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9823,7 +9820,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9841,13 +9838,13 @@
         <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>81</v>
@@ -9855,14 +9852,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9881,13 +9878,13 @@
         <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9938,7 +9935,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9953,31 +9950,31 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AL65" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="AL65" t="s" s="2">
+      <c r="AM65" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="AM65" t="s" s="2">
+      <c r="AN65" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="AN65" t="s" s="2">
+      <c r="AO65" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>492</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9996,13 +9993,13 @@
         <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10041,17 +10038,17 @@
         <v>81</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AC66" s="2"/>
       <c r="AD66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10066,33 +10063,33 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AL66" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="AL66" t="s" s="2">
+      <c r="AM66" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AN66" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="AN66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>503</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="C67" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="B67" t="s" s="2">
+      <c r="D67" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="D67" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10111,13 +10108,13 @@
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10168,7 +10165,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10183,27 +10180,27 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AL67" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="AL67" t="s" s="2">
+      <c r="AM67" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="AM67" t="s" s="2">
+      <c r="AN67" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>503</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10226,13 +10223,13 @@
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10259,14 +10256,14 @@
         <v>81</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="Z68" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="Z68" t="s" s="2">
-        <v>512</v>
-      </c>
       <c r="AA68" t="s" s="2">
         <v>81</v>
       </c>
@@ -10283,7 +10280,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10307,22 +10304,22 @@
         <v>81</v>
       </c>
       <c r="AN68" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>514</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10341,13 +10338,13 @@
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10398,7 +10395,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10413,31 +10410,31 @@
         <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AL69" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="AL69" t="s" s="2">
+      <c r="AM69" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AN69" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>523</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10456,16 +10453,16 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10515,7 +10512,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10530,31 +10527,31 @@
         <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AL70" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="AL70" t="s" s="2">
+      <c r="AM70" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AN70" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="AN70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>534</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10573,16 +10570,16 @@
         <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10608,14 +10605,14 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="Z71" t="s" s="2">
-        <v>541</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
       </c>
@@ -10632,7 +10629,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10647,16 +10644,16 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AL71" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="AL71" t="s" s="2">
+      <c r="AM71" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="AM71" t="s" s="2">
+      <c r="AN71" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>81</v>
@@ -10664,14 +10661,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10690,16 +10687,16 @@
         <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10749,7 +10746,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10764,16 +10761,16 @@
         <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="AL72" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AN72" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>81</v>
@@ -10781,10 +10778,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10807,13 +10804,13 @@
         <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10840,14 +10837,14 @@
         <v>81</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Y73" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="Z73" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="Z73" t="s" s="2">
-        <v>560</v>
-      </c>
       <c r="AA73" t="s" s="2">
         <v>81</v>
       </c>
@@ -10864,7 +10861,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10882,13 +10879,13 @@
         <v>81</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>81</v>
@@ -10896,10 +10893,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10922,16 +10919,16 @@
         <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10957,14 +10954,14 @@
         <v>81</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="Z74" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="Z74" t="s" s="2">
-        <v>568</v>
-      </c>
       <c r="AA74" t="s" s="2">
         <v>81</v>
       </c>
@@ -10981,7 +10978,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10996,16 +10993,16 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AL74" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="AL74" t="s" s="2">
+      <c r="AM74" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AN74" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>81</v>
@@ -11013,10 +11010,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11039,13 +11036,13 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11096,7 +11093,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11111,16 +11108,16 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM75" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="AL75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM75" t="s" s="2">
+      <c r="AN75" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>81</v>
@@ -11128,14 +11125,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11154,16 +11151,16 @@
         <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11213,7 +11210,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11228,16 +11225,16 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="AL76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM76" t="s" s="2">
+      <c r="AN76" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>81</v>
@@ -11245,10 +11242,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11271,16 +11268,16 @@
         <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11330,7 +11327,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11351,10 +11348,10 @@
         <v>81</v>
       </c>
       <c r="AM77" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>81</v>
@@ -11362,14 +11359,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11388,19 +11385,19 @@
         <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -11425,14 +11422,14 @@
         <v>81</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Y78" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="Z78" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="Z78" t="s" s="2">
-        <v>603</v>
-      </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
       </c>
@@ -11449,7 +11446,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11458,7 +11455,7 @@
         <v>80</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>102</v>
@@ -11470,25 +11467,25 @@
         <v>81</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AN78" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AO78" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>606</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11507,17 +11504,17 @@
         <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="L79" t="s" s="2">
-        <v>610</v>
-      </c>
       <c r="M79" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>81</v>
@@ -11566,7 +11563,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11575,7 +11572,7 @@
         <v>90</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>102</v>
@@ -11587,21 +11584,21 @@
         <v>81</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11624,13 +11621,13 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="L80" t="s" s="2">
         <v>50</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11681,7 +11678,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11696,27 +11693,27 @@
         <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="AL80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="AN80" t="s" s="2">
+      <c r="AO80" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>617</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11739,13 +11736,13 @@
         <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11796,7 +11793,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11817,10 +11814,10 @@
         <v>81</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>81</v>
@@ -11828,10 +11825,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11854,7 +11851,7 @@
         <v>81</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L82" t="s" s="2">
         <v>166</v>
@@ -11943,10 +11940,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12028,7 +12025,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12060,14 +12057,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12089,10 +12086,10 @@
         <v>138</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>141</v>
@@ -12147,7 +12144,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12179,10 +12176,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12205,13 +12202,13 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12262,7 +12259,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12283,10 +12280,10 @@
         <v>81</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>81</v>
@@ -12294,10 +12291,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12320,16 +12317,16 @@
         <v>81</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12379,7 +12376,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12394,7 +12391,7 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>81</v>
@@ -12403,7 +12400,7 @@
         <v>135</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>81</v>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:16+00:00</t>
+    <t>2023-05-11T10:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:44+00:00</t>
+    <t>2023-05-11T11:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:14:34+00:00</t>
+    <t>2023-05-11T11:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/HIV-lab-order</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/HIV-lab-order</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:21:30+00:00</t>
+    <t>2023-05-11T11:55:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1270,7 +1270,7 @@
     <t>Many laboratory and radiology procedure codes embed the specimen/organ system in the test order name, for example,  serum or serum/plasma glucose, or a chest x-ray. The specimen might not be recorded separately from the test code.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-test-types</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/ValueSet/vs-test-types</t>
   </si>
   <si>
     <t xml:space="preserve">prr-1
@@ -2343,7 +2343,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="126.34765625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.80078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="100.84765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:55:17+00:00</t>
+    <t>2023-05-11T12:03:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/HIV-lab-order</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/HIV-lab-order</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:03:20+00:00</t>
+    <t>2023-05-11T12:08:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1270,7 +1270,7 @@
     <t>Many laboratory and radiology procedure codes embed the specimen/organ system in the test order name, for example,  serum or serum/plasma glucose, or a chest x-ray. The specimen might not be recorded separately from the test code.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/ValueSet/vs-test-types</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-test-types</t>
   </si>
   <si>
     <t xml:space="preserve">prr-1
@@ -2343,7 +2343,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="126.34765625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="100.84765625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.80078125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:08:48+00:00</t>
+    <t>2023-05-11T12:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:16:35+00:00</t>
+    <t>2023-05-11T12:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:20:22+00:00</t>
+    <t>2023-05-11T12:21:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:21:18+00:00</t>
+    <t>2023-05-11T15:25:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T15:25:42+00:00</t>
+    <t>2023-05-11T15:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T15:26:02+00:00</t>
+    <t>2023-05-11T16:43:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:02+00:00</t>
+    <t>2023-05-11T16:43:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:55+00:00</t>
+    <t>2023-05-11T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:57:46+00:00</t>
+    <t>2023-05-11T16:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:58:30+00:00</t>
+    <t>2023-05-11T17:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:02+00:00</t>
+    <t>2023-05-11T17:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/HIV-lab-order</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/HIV-lab-order</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:30+00:00</t>
+    <t>2023-05-11T18:15:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1270,7 +1270,7 @@
     <t>Many laboratory and radiology procedure codes embed the specimen/organ system in the test order name, for example,  serum or serum/plasma glucose, or a chest x-ray. The specimen might not be recorded separately from the test code.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-test-types</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/ValueSet/vs-test-types</t>
   </si>
   <si>
     <t xml:space="preserve">prr-1
@@ -2343,7 +2343,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="126.34765625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.80078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="96.515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:15:51+00:00</t>
+    <t>2023-05-11T18:16:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/HIV-lab-order</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/HIV-lab-order</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:16:31+00:00</t>
+    <t>2023-05-11T18:27:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1270,7 +1270,7 @@
     <t>Many laboratory and radiology procedure codes embed the specimen/organ system in the test order name, for example,  serum or serum/plasma glucose, or a chest x-ray. The specimen might not be recorded separately from the test code.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/ValueSet/vs-test-types</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-test-types</t>
   </si>
   <si>
     <t xml:space="preserve">prr-1
@@ -2343,7 +2343,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="126.34765625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="96.515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.80078125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:27:59+00:00</t>
+    <t>2023-05-11T18:29:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:29:46+00:00</t>
+    <t>2023-05-11T18:48:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:48:31+00:00</t>
+    <t>2023-05-11T18:54:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:54:41+00:00</t>
+    <t>2023-05-11T19:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:41:30+00:00</t>
+    <t>2023-05-11T19:42:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:42:15+00:00</t>
+    <t>2023-05-11T20:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:23:29+00:00</t>
+    <t>2023-05-11T20:24:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:24:51+00:00</t>
+    <t>2023-05-12T02:48:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:48:54+00:00</t>
+    <t>2023-05-12T02:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:49:37+00:00</t>
+    <t>2023-05-12T07:30:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:25+00:00</t>
+    <t>2023-05-12T07:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:35+00:00</t>
+    <t>2023-05-12T07:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:36:14+00:00</t>
+    <t>2023-05-12T07:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:36:30+00:00</t>
+    <t>2023-05-12T07:54:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:54:06+00:00</t>
+    <t>2023-05-12T07:55:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:55:51+00:00</t>
+    <t>2023-05-12T10:26:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:26:59+00:00</t>
+    <t>2023-05-12T10:27:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:27:50+00:00</t>
+    <t>2023-05-12T10:32:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:32:06+00:00</t>
+    <t>2023-05-12T10:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:40:31+00:00</t>
+    <t>2023-05-12T13:37:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:37:18+00:00</t>
+    <t>2023-05-12T13:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:51:30+00:00</t>
+    <t>2023-05-23T09:07:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T09:07:38+00:00</t>
+    <t>2023-05-23T09:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
